--- a/KindleClippings.ConsoleApp/GooglePhotoAlbums.xlsx
+++ b/KindleClippings.ConsoleApp/GooglePhotoAlbums.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alber\Documents\Visual Studio 2022\Projects\AlbertoBizzini\KindleClippings.ConsoleApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E276D0AC-A2D8-4879-8DB3-FE42EE8B2BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AE3743-AECC-4CFA-84D8-6B237FE38299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10452" yWindow="1632" windowWidth="23004" windowHeight="12084" activeTab="1" xr2:uid="{23D7D280-0862-40F4-B544-C752C03DD8BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" activeTab="1" xr2:uid="{23D7D280-0862-40F4-B544-C752C03DD8BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Albums" sheetId="1" r:id="rId1"/>
     <sheet name="AlbumLocations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">AlbumLocations!$A$1:$I$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">AlbumLocations!$A$1:$I$358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Albums!$A$1:$F$315</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="1494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="1498">
   <si>
     <t>AlbumId</t>
   </si>
@@ -4506,6 +4507,18 @@
   </si>
   <si>
     <t>Iwakuni</t>
+  </si>
+  <si>
+    <t>https://photos.app.goo.gl/BxUfvcc9BHM3ubBZ8</t>
+  </si>
+  <si>
+    <t>https://photos.google.com/share/AF1QipPAJp8kGyMJL5cA1XOBqaOvOwK-HbZ2Lgw6QWV55xORLcJEgxeV2zJILBfiCF1vdA?key=c3VmeDFTeHBoWk1QaHVrWXBTU2FacEowUURuZkp3</t>
+  </si>
+  <si>
+    <t>Orologio da parete in stile giapponese</t>
+  </si>
+  <si>
+    <t>album-0315</t>
   </si>
 </sst>
 </file>
@@ -4513,8 +4526,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -5002,11 +5015,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5052,7 +5066,60 @@
     <cellStyle name="Valore non valido" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Valore valido" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="9"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="9"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5063,6 +5130,53 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F24003B8-F290-4722-846F-9F5CB5585298}" name="Albums" displayName="Albums" ref="A1:F316" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F316" xr:uid="{F24003B8-F290-4722-846F-9F5CB5585298}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Arredi per Mezzocorona"/>
+        <filter val="Costruzione orologio per Roberta"/>
+        <filter val="Orologio da parete in stile &quot;yoga&quot;"/>
+        <filter val="Orologio da parete in stile giapponese"/>
+        <filter val="Riparazione danno da &quot;kickback&quot; su orologio yoga"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C1F48587-0B9D-436C-ACF4-6B39FD646AA4}" name="AlbumId"/>
+    <tableColumn id="2" xr3:uid="{4BD37CF8-4A9A-405D-8EC8-FF4B8C738AA9}" name="Data da"/>
+    <tableColumn id="3" xr3:uid="{FFA2E74F-ADEA-456C-B9DB-48BB86058F68}" name="Data a"/>
+    <tableColumn id="4" xr3:uid="{B26773FA-08B1-41CC-A5DF-111FB8D495A1}" name="Titolo"/>
+    <tableColumn id="5" xr3:uid="{5A0A2A68-9675-4087-A413-8E47867EDCFD}" name="URL pubblico"/>
+    <tableColumn id="6" xr3:uid="{FDBA3496-A032-4D45-B50F-31C78B858A99}" name="URL album"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52AACAD4-B883-4C4A-8F1A-2B8CD5DD089D}" name="AlbumLocations" displayName="AlbumLocations" ref="A1:I358" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I358" xr:uid="{26718399-4DCE-4947-A696-7F3D21958683}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I358">
+    <sortCondition ref="A2:A358"/>
+    <sortCondition ref="B2:B358"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{0429AB00-90EC-4BEF-B6E6-835ED3368FF8}" name="AlbumId"/>
+    <tableColumn id="2" xr3:uid="{23CFEC90-303E-4FBC-BCC3-464DBC3FB2CD}" name="Order"/>
+    <tableColumn id="3" xr3:uid="{386C19B6-FC6D-4EB8-A67F-3108AA76A5B0}" name="Continente"/>
+    <tableColumn id="4" xr3:uid="{74B26627-9EA0-4481-A202-64E8EF3FB7BA}" name="Luogo (nazione)"/>
+    <tableColumn id="5" xr3:uid="{455A045C-F9A0-44F2-8789-AFF0CE7D09C7}" name="Luogo (nazione) - English"/>
+    <tableColumn id="6" xr3:uid="{020557AB-CE42-425D-A512-A9ECFAA1E7EF}" name="Luogo (città)"/>
+    <tableColumn id="7" xr3:uid="{05B2AFE8-7E66-49C2-85B5-8546E150F1FB}" name="Luogo (città) - English"/>
+    <tableColumn id="8" xr3:uid="{EE443166-26EE-48FD-A800-87409EA19E1D}" name="Luogo (Latitudine)" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{656EDC5A-359E-495C-8F69-7C098937F3A7}" name="Luogo (Longitudine)" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5382,13 +5496,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9EF91B6-FA02-4FAE-A7C7-1F838D2DC00C}">
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F316"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="61.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="51.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="157.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -5411,7 +5526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -5431,7 +5546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5451,7 +5566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5471,7 +5586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5491,7 +5606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -5508,7 +5623,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -5525,7 +5640,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -5545,7 +5660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -5565,7 +5680,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -5582,7 +5697,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -5602,7 +5717,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -5622,7 +5737,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -5642,7 +5757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -5662,7 +5777,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -5682,7 +5797,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>59</v>
       </c>
@@ -5702,7 +5817,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -5722,7 +5837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -5742,7 +5857,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -5762,7 +5877,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -5782,7 +5897,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -5802,7 +5917,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>83</v>
       </c>
@@ -5822,7 +5937,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -5842,7 +5957,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>91</v>
       </c>
@@ -5862,7 +5977,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -5882,7 +5997,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>99</v>
       </c>
@@ -5902,7 +6017,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -5922,7 +6037,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -5942,7 +6057,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>111</v>
       </c>
@@ -5962,7 +6077,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -5982,7 +6097,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -6002,7 +6117,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -6022,7 +6137,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -6042,7 +6157,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -6062,7 +6177,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>135</v>
       </c>
@@ -6082,7 +6197,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>139</v>
       </c>
@@ -6102,7 +6217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>143</v>
       </c>
@@ -6122,7 +6237,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>147</v>
       </c>
@@ -6142,7 +6257,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>151</v>
       </c>
@@ -6162,7 +6277,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>155</v>
       </c>
@@ -6182,7 +6297,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>159</v>
       </c>
@@ -6202,7 +6317,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>163</v>
       </c>
@@ -6219,7 +6334,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>166</v>
       </c>
@@ -6239,7 +6354,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>170</v>
       </c>
@@ -6259,7 +6374,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>174</v>
       </c>
@@ -6279,7 +6394,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>178</v>
       </c>
@@ -6299,7 +6414,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>182</v>
       </c>
@@ -6319,7 +6434,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>186</v>
       </c>
@@ -6339,7 +6454,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>190</v>
       </c>
@@ -6359,7 +6474,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>194</v>
       </c>
@@ -6379,7 +6494,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>198</v>
       </c>
@@ -6399,7 +6514,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>202</v>
       </c>
@@ -6419,7 +6534,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>206</v>
       </c>
@@ -6439,7 +6554,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>210</v>
       </c>
@@ -6459,7 +6574,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>214</v>
       </c>
@@ -6479,7 +6594,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -6499,7 +6614,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -6519,7 +6634,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>226</v>
       </c>
@@ -6539,7 +6654,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>230</v>
       </c>
@@ -6559,7 +6674,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>234</v>
       </c>
@@ -6579,7 +6694,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>238</v>
       </c>
@@ -6599,7 +6714,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>242</v>
       </c>
@@ -6619,7 +6734,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>246</v>
       </c>
@@ -6636,7 +6751,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>249</v>
       </c>
@@ -6656,7 +6771,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>253</v>
       </c>
@@ -6676,7 +6791,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>257</v>
       </c>
@@ -6696,7 +6811,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>261</v>
       </c>
@@ -6716,7 +6831,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>265</v>
       </c>
@@ -6736,7 +6851,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>269</v>
       </c>
@@ -6756,7 +6871,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>273</v>
       </c>
@@ -6776,7 +6891,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>277</v>
       </c>
@@ -6796,7 +6911,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>281</v>
       </c>
@@ -6816,7 +6931,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>285</v>
       </c>
@@ -6836,7 +6951,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>289</v>
       </c>
@@ -6856,7 +6971,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>293</v>
       </c>
@@ -6876,7 +6991,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>297</v>
       </c>
@@ -6896,7 +7011,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>301</v>
       </c>
@@ -6916,7 +7031,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>305</v>
       </c>
@@ -6936,7 +7051,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>309</v>
       </c>
@@ -6956,7 +7071,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>313</v>
       </c>
@@ -6976,7 +7091,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>317</v>
       </c>
@@ -6996,7 +7111,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>321</v>
       </c>
@@ -7016,7 +7131,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>325</v>
       </c>
@@ -7033,7 +7148,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>328</v>
       </c>
@@ -7053,7 +7168,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>332</v>
       </c>
@@ -7073,7 +7188,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>336</v>
       </c>
@@ -7093,7 +7208,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>340</v>
       </c>
@@ -7113,7 +7228,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>344</v>
       </c>
@@ -7133,7 +7248,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>348</v>
       </c>
@@ -7153,7 +7268,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>352</v>
       </c>
@@ -7173,7 +7288,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>356</v>
       </c>
@@ -7193,7 +7308,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>360</v>
       </c>
@@ -7213,7 +7328,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>364</v>
       </c>
@@ -7233,7 +7348,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>368</v>
       </c>
@@ -7253,7 +7368,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>372</v>
       </c>
@@ -7273,7 +7388,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>376</v>
       </c>
@@ -7293,7 +7408,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>380</v>
       </c>
@@ -7313,7 +7428,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>384</v>
       </c>
@@ -7333,7 +7448,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>388</v>
       </c>
@@ -7353,7 +7468,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>392</v>
       </c>
@@ -7373,7 +7488,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>396</v>
       </c>
@@ -7393,7 +7508,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>400</v>
       </c>
@@ -7413,7 +7528,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>404</v>
       </c>
@@ -7433,7 +7548,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>408</v>
       </c>
@@ -7453,7 +7568,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>412</v>
       </c>
@@ -7473,7 +7588,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>416</v>
       </c>
@@ -7493,7 +7608,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>420</v>
       </c>
@@ -7513,7 +7628,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>424</v>
       </c>
@@ -7533,7 +7648,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>428</v>
       </c>
@@ -7553,7 +7668,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>432</v>
       </c>
@@ -7573,7 +7688,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>436</v>
       </c>
@@ -7593,7 +7708,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>440</v>
       </c>
@@ -7610,7 +7725,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>443</v>
       </c>
@@ -7630,7 +7745,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>447</v>
       </c>
@@ -7647,7 +7762,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>450</v>
       </c>
@@ -7664,7 +7779,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>453</v>
       </c>
@@ -7684,7 +7799,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>457</v>
       </c>
@@ -7704,7 +7819,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>461</v>
       </c>
@@ -7721,7 +7836,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>464</v>
       </c>
@@ -7741,7 +7856,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>468</v>
       </c>
@@ -7761,7 +7876,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>472</v>
       </c>
@@ -7781,7 +7896,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>476</v>
       </c>
@@ -7801,7 +7916,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>480</v>
       </c>
@@ -7821,7 +7936,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>484</v>
       </c>
@@ -7841,7 +7956,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>488</v>
       </c>
@@ -7861,7 +7976,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>492</v>
       </c>
@@ -7881,7 +7996,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>496</v>
       </c>
@@ -7901,7 +8016,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>500</v>
       </c>
@@ -7921,7 +8036,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>504</v>
       </c>
@@ -7941,7 +8056,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>508</v>
       </c>
@@ -7961,7 +8076,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>512</v>
       </c>
@@ -7981,7 +8096,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>516</v>
       </c>
@@ -8001,7 +8116,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>520</v>
       </c>
@@ -8021,7 +8136,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>524</v>
       </c>
@@ -8041,7 +8156,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>528</v>
       </c>
@@ -8061,7 +8176,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>532</v>
       </c>
@@ -8081,7 +8196,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>536</v>
       </c>
@@ -8101,7 +8216,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>540</v>
       </c>
@@ -8121,7 +8236,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>544</v>
       </c>
@@ -8141,7 +8256,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>548</v>
       </c>
@@ -8158,7 +8273,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>551</v>
       </c>
@@ -8178,7 +8293,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>555</v>
       </c>
@@ -8198,7 +8313,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>559</v>
       </c>
@@ -8218,7 +8333,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>563</v>
       </c>
@@ -8238,7 +8353,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>567</v>
       </c>
@@ -8258,7 +8373,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>571</v>
       </c>
@@ -8278,7 +8393,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>575</v>
       </c>
@@ -8298,7 +8413,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>579</v>
       </c>
@@ -8318,7 +8433,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>583</v>
       </c>
@@ -8338,7 +8453,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>587</v>
       </c>
@@ -8358,7 +8473,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>591</v>
       </c>
@@ -8378,7 +8493,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>595</v>
       </c>
@@ -8398,7 +8513,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>599</v>
       </c>
@@ -8418,7 +8533,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>603</v>
       </c>
@@ -8438,7 +8553,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>607</v>
       </c>
@@ -8455,7 +8570,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>610</v>
       </c>
@@ -8475,7 +8590,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>614</v>
       </c>
@@ -8495,7 +8610,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>618</v>
       </c>
@@ -8515,7 +8630,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>622</v>
       </c>
@@ -8535,7 +8650,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>626</v>
       </c>
@@ -8555,7 +8670,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>630</v>
       </c>
@@ -8572,7 +8687,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>633</v>
       </c>
@@ -8592,7 +8707,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>637</v>
       </c>
@@ -8609,7 +8724,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>640</v>
       </c>
@@ -8629,7 +8744,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>644</v>
       </c>
@@ -8669,7 +8784,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>652</v>
       </c>
@@ -8689,7 +8804,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>656</v>
       </c>
@@ -8709,7 +8824,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>660</v>
       </c>
@@ -8729,7 +8844,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>664</v>
       </c>
@@ -8749,7 +8864,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>668</v>
       </c>
@@ -8769,7 +8884,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>672</v>
       </c>
@@ -8789,7 +8904,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>676</v>
       </c>
@@ -8809,7 +8924,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>680</v>
       </c>
@@ -8829,7 +8944,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>684</v>
       </c>
@@ -8849,7 +8964,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>688</v>
       </c>
@@ -8869,7 +8984,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>692</v>
       </c>
@@ -8889,7 +9004,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>696</v>
       </c>
@@ -8909,7 +9024,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>700</v>
       </c>
@@ -8929,7 +9044,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>704</v>
       </c>
@@ -8949,7 +9064,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>708</v>
       </c>
@@ -8966,7 +9081,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>711</v>
       </c>
@@ -8986,7 +9101,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>715</v>
       </c>
@@ -9006,7 +9121,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>719</v>
       </c>
@@ -9026,7 +9141,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>723</v>
       </c>
@@ -9046,7 +9161,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>727</v>
       </c>
@@ -9063,7 +9178,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>730</v>
       </c>
@@ -9080,7 +9195,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>733</v>
       </c>
@@ -9100,7 +9215,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>737</v>
       </c>
@@ -9120,7 +9235,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>741</v>
       </c>
@@ -9140,7 +9255,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>745</v>
       </c>
@@ -9160,7 +9275,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>749</v>
       </c>
@@ -9180,7 +9295,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>753</v>
       </c>
@@ -9200,7 +9315,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>757</v>
       </c>
@@ -9220,7 +9335,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>761</v>
       </c>
@@ -9240,7 +9355,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>765</v>
       </c>
@@ -9260,7 +9375,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>769</v>
       </c>
@@ -9280,7 +9395,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>773</v>
       </c>
@@ -9300,7 +9415,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>777</v>
       </c>
@@ -9320,7 +9435,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>781</v>
       </c>
@@ -9340,7 +9455,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>785</v>
       </c>
@@ -9360,7 +9475,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>789</v>
       </c>
@@ -9380,7 +9495,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>793</v>
       </c>
@@ -9400,7 +9515,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>797</v>
       </c>
@@ -9420,7 +9535,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>801</v>
       </c>
@@ -9440,7 +9555,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>805</v>
       </c>
@@ -9500,7 +9615,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>817</v>
       </c>
@@ -9520,7 +9635,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>821</v>
       </c>
@@ -9540,7 +9655,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>825</v>
       </c>
@@ -9560,7 +9675,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>829</v>
       </c>
@@ -9580,7 +9695,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>833</v>
       </c>
@@ -9600,7 +9715,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>837</v>
       </c>
@@ -9620,7 +9735,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>841</v>
       </c>
@@ -9640,7 +9755,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>845</v>
       </c>
@@ -9657,7 +9772,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>848</v>
       </c>
@@ -9677,7 +9792,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>852</v>
       </c>
@@ -9697,7 +9812,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>856</v>
       </c>
@@ -9717,7 +9832,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>860</v>
       </c>
@@ -9737,7 +9852,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>864</v>
       </c>
@@ -9757,7 +9872,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>868</v>
       </c>
@@ -9777,7 +9892,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>872</v>
       </c>
@@ -9797,7 +9912,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>876</v>
       </c>
@@ -9814,7 +9929,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>879</v>
       </c>
@@ -9834,7 +9949,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>883</v>
       </c>
@@ -9854,7 +9969,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>887</v>
       </c>
@@ -9874,7 +9989,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>891</v>
       </c>
@@ -9894,7 +10009,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>895</v>
       </c>
@@ -9911,7 +10026,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>898</v>
       </c>
@@ -9931,7 +10046,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>902</v>
       </c>
@@ -9948,7 +10063,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>905</v>
       </c>
@@ -9968,7 +10083,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>909</v>
       </c>
@@ -9988,7 +10103,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>913</v>
       </c>
@@ -10008,7 +10123,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>917</v>
       </c>
@@ -10028,7 +10143,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>921</v>
       </c>
@@ -10048,7 +10163,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>925</v>
       </c>
@@ -10068,7 +10183,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>929</v>
       </c>
@@ -10088,7 +10203,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>933</v>
       </c>
@@ -10108,7 +10223,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>937</v>
       </c>
@@ -10128,7 +10243,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>941</v>
       </c>
@@ -10148,7 +10263,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>945</v>
       </c>
@@ -10165,7 +10280,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>948</v>
       </c>
@@ -10182,7 +10297,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>951</v>
       </c>
@@ -10202,7 +10317,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>955</v>
       </c>
@@ -10222,7 +10337,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>959</v>
       </c>
@@ -10242,7 +10357,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>963</v>
       </c>
@@ -10262,7 +10377,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>967</v>
       </c>
@@ -10282,7 +10397,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>971</v>
       </c>
@@ -10302,7 +10417,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>975</v>
       </c>
@@ -10322,7 +10437,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>979</v>
       </c>
@@ -10342,7 +10457,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>983</v>
       </c>
@@ -10362,7 +10477,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>987</v>
       </c>
@@ -10382,7 +10497,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>991</v>
       </c>
@@ -10402,7 +10517,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>995</v>
       </c>
@@ -10422,7 +10537,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>999</v>
       </c>
@@ -10442,7 +10557,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1003</v>
       </c>
@@ -10462,7 +10577,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1007</v>
       </c>
@@ -10482,7 +10597,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1011</v>
       </c>
@@ -10499,7 +10614,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1014</v>
       </c>
@@ -10519,7 +10634,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1018</v>
       </c>
@@ -10539,7 +10654,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1022</v>
       </c>
@@ -10556,7 +10671,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1025</v>
       </c>
@@ -10576,7 +10691,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1029</v>
       </c>
@@ -10596,7 +10711,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1033</v>
       </c>
@@ -10613,7 +10728,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>1036</v>
       </c>
@@ -10633,7 +10748,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1040</v>
       </c>
@@ -10653,7 +10768,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1044</v>
       </c>
@@ -10673,7 +10788,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1048</v>
       </c>
@@ -10693,7 +10808,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1052</v>
       </c>
@@ -10713,7 +10828,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1056</v>
       </c>
@@ -10733,7 +10848,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1060</v>
       </c>
@@ -10753,7 +10868,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1064</v>
       </c>
@@ -10770,7 +10885,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1067</v>
       </c>
@@ -10787,7 +10902,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1070</v>
       </c>
@@ -10807,7 +10922,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1074</v>
       </c>
@@ -10827,7 +10942,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1078</v>
       </c>
@@ -10844,7 +10959,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1081</v>
       </c>
@@ -10875,7 +10990,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1087</v>
       </c>
@@ -10895,7 +11010,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1091</v>
       </c>
@@ -10915,7 +11030,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1095</v>
       </c>
@@ -10935,7 +11050,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1099</v>
       </c>
@@ -10955,7 +11070,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1103</v>
       </c>
@@ -10975,7 +11090,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1107</v>
       </c>
@@ -10995,7 +11110,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1111</v>
       </c>
@@ -11015,7 +11130,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1115</v>
       </c>
@@ -11035,7 +11150,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>1119</v>
       </c>
@@ -11055,7 +11170,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1123</v>
       </c>
@@ -11075,7 +11190,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1127</v>
       </c>
@@ -11095,7 +11210,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1131</v>
       </c>
@@ -11115,7 +11230,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1135</v>
       </c>
@@ -11135,7 +11250,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>1139</v>
       </c>
@@ -11155,7 +11270,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1143</v>
       </c>
@@ -11175,7 +11290,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1147</v>
       </c>
@@ -11195,7 +11310,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1151</v>
       </c>
@@ -11215,7 +11330,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1155</v>
       </c>
@@ -11235,7 +11350,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>1159</v>
       </c>
@@ -11252,7 +11367,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1162</v>
       </c>
@@ -11272,7 +11387,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1166</v>
       </c>
@@ -11283,7 +11398,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1169</v>
       </c>
@@ -11294,7 +11409,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1172</v>
       </c>
@@ -11305,7 +11420,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1175</v>
       </c>
@@ -11316,7 +11431,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1178</v>
       </c>
@@ -11327,7 +11442,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1181</v>
       </c>
@@ -11338,7 +11453,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1184</v>
       </c>
@@ -11349,7 +11464,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1187</v>
       </c>
@@ -11360,7 +11475,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1190</v>
       </c>
@@ -11371,7 +11486,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1193</v>
       </c>
@@ -11382,7 +11497,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1196</v>
       </c>
@@ -11393,7 +11508,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1199</v>
       </c>
@@ -11404,7 +11519,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1202</v>
       </c>
@@ -11415,7 +11530,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1205</v>
       </c>
@@ -11426,7 +11541,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1208</v>
       </c>
@@ -11437,7 +11552,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1211</v>
       </c>
@@ -11448,14 +11563,37 @@
         <v>1213</v>
       </c>
     </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B316" s="4">
+        <v>46198</v>
+      </c>
+      <c r="C316" s="4">
+        <v>46198</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E316" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F316" t="s">
+        <v>1495</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26718399-4DCE-4947-A696-7F3D21958683}">
-  <dimension ref="A1:I357"/>
+  <dimension ref="A1:I358"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -21598,8 +21736,39 @@
         <v>-5.5624000000000002</v>
       </c>
     </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B358">
+        <v>1</v>
+      </c>
+      <c r="C358" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D358" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E358" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F358" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G358" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H358" s="3">
+        <v>44.509300000000003</v>
+      </c>
+      <c r="I358" s="3">
+        <v>11.3589</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I357" xr:uid="{26718399-4DCE-4947-A696-7F3D21958683}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>